--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382246</v>
+        <v>125382079</v>
       </c>
       <c r="B2" t="n">
-        <v>98124</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720893</v>
+        <v>720903</v>
       </c>
       <c r="R2" t="n">
-        <v>6361820</v>
+        <v>6361878</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +762,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök i död tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,11 +775,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -903,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125382244</v>
+        <v>125382250</v>
       </c>
       <c r="B4" t="n">
         <v>98124</v>
@@ -938,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720878</v>
+        <v>720917</v>
       </c>
       <c r="R4" t="n">
-        <v>6361800</v>
+        <v>6361832</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1024,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125382250</v>
+        <v>125382252</v>
       </c>
       <c r="B5" t="n">
         <v>98124</v>
@@ -1059,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1078,10 +1073,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720917</v>
+        <v>720924</v>
       </c>
       <c r="R5" t="n">
-        <v>6361832</v>
+        <v>6361826</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1145,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125382079</v>
+        <v>125382263</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98123</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,25 +1152,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1183,9 +1178,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720903</v>
+        <v>720892</v>
       </c>
       <c r="R6" t="n">
-        <v>6361878</v>
+        <v>6361887</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,11 +1232,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosök i död tall</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1245,6 +1240,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125382252</v>
+        <v>125382246</v>
       </c>
       <c r="B7" t="n">
         <v>98124</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720924</v>
+        <v>720893</v>
       </c>
       <c r="R7" t="n">
-        <v>6361826</v>
+        <v>6361820</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125382263</v>
+        <v>125382244</v>
       </c>
       <c r="B8" t="n">
-        <v>98123</v>
+        <v>98124</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,26 +1398,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720892</v>
+        <v>720878</v>
       </c>
       <c r="R8" t="n">
-        <v>6361887</v>
+        <v>6361800</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382079</v>
+        <v>125382250</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720903</v>
+        <v>720917</v>
       </c>
       <c r="R2" t="n">
-        <v>6361878</v>
+        <v>6361832</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,11 +767,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök i död tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +775,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125382243</v>
+        <v>125382244</v>
       </c>
       <c r="B3" t="n">
-        <v>105676</v>
+        <v>98124</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,28 +808,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
@@ -898,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125382250</v>
+        <v>125382079</v>
       </c>
       <c r="B4" t="n">
-        <v>98124</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,40 +929,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -952,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720917</v>
+        <v>720903</v>
       </c>
       <c r="R4" t="n">
-        <v>6361832</v>
+        <v>6361878</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,6 +1004,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosök i död tall</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -998,11 +1017,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1019,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125382252</v>
+        <v>125382263</v>
       </c>
       <c r="B5" t="n">
-        <v>98124</v>
+        <v>98123</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,21 +1049,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,7 +1078,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1073,13 +1087,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720924</v>
+        <v>720892</v>
       </c>
       <c r="R5" t="n">
-        <v>6361826</v>
+        <v>6361887</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125382263</v>
+        <v>125382252</v>
       </c>
       <c r="B6" t="n">
-        <v>98123</v>
+        <v>98124</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1170,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1185,7 +1199,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,13 +1208,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720892</v>
+        <v>720924</v>
       </c>
       <c r="R6" t="n">
-        <v>6361887</v>
+        <v>6361826</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125382246</v>
+        <v>125382243</v>
       </c>
       <c r="B7" t="n">
-        <v>98124</v>
+        <v>105676</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,52 +1287,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720893</v>
+        <v>720878</v>
       </c>
       <c r="R7" t="n">
-        <v>6361820</v>
+        <v>6361800</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125382244</v>
+        <v>125382246</v>
       </c>
       <c r="B8" t="n">
         <v>98124</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720878</v>
+        <v>720893</v>
       </c>
       <c r="R8" t="n">
-        <v>6361800</v>
+        <v>6361820</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382250</v>
+        <v>125382263</v>
       </c>
       <c r="B2" t="n">
-        <v>98124</v>
+        <v>98291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720917</v>
+        <v>720892</v>
       </c>
       <c r="R2" t="n">
-        <v>6361832</v>
+        <v>6361887</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125382244</v>
+        <v>125382246</v>
       </c>
       <c r="B3" t="n">
-        <v>98124</v>
+        <v>98292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720878</v>
+        <v>720893</v>
       </c>
       <c r="R3" t="n">
-        <v>6361800</v>
+        <v>6361820</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125382079</v>
+        <v>125382244</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,35 +929,40 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720903</v>
+        <v>720878</v>
       </c>
       <c r="R4" t="n">
-        <v>6361878</v>
+        <v>6361800</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1004,11 +1009,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födosök i död tall</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1017,6 +1017,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1033,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125382263</v>
+        <v>125382243</v>
       </c>
       <c r="B5" t="n">
-        <v>98123</v>
+        <v>105853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,55 +1050,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720892</v>
+        <v>720878</v>
       </c>
       <c r="R5" t="n">
-        <v>6361887</v>
+        <v>6361800</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,7 +1148,7 @@
         <v>125382252</v>
       </c>
       <c r="B6" t="n">
-        <v>98124</v>
+        <v>98292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1275,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125382243</v>
+        <v>125382250</v>
       </c>
       <c r="B7" t="n">
-        <v>105676</v>
+        <v>98292</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,38 +1278,52 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720878</v>
+        <v>720917</v>
       </c>
       <c r="R7" t="n">
-        <v>6361800</v>
+        <v>6361832</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1382,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125382246</v>
+        <v>125382079</v>
       </c>
       <c r="B8" t="n">
-        <v>98124</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,40 +1399,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720893</v>
+        <v>720903</v>
       </c>
       <c r="R8" t="n">
-        <v>6361820</v>
+        <v>6361878</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,6 +1474,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosök i död tall</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1482,11 +1487,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382263</v>
+        <v>125382246</v>
       </c>
       <c r="B2" t="n">
-        <v>98291</v>
+        <v>98292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720892</v>
+        <v>720893</v>
       </c>
       <c r="R2" t="n">
-        <v>6361887</v>
+        <v>6361820</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125382246</v>
+        <v>125382079</v>
       </c>
       <c r="B3" t="n">
-        <v>98292</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,40 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720893</v>
+        <v>720903</v>
       </c>
       <c r="R3" t="n">
-        <v>6361820</v>
+        <v>6361878</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -888,6 +883,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök i död tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,11 +896,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125382244</v>
+        <v>125382263</v>
       </c>
       <c r="B4" t="n">
-        <v>98292</v>
+        <v>98291</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,26 +928,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -962,7 +957,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,13 +966,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720878</v>
+        <v>720892</v>
       </c>
       <c r="R4" t="n">
-        <v>6361800</v>
+        <v>6361887</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1038,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125382243</v>
+        <v>125382244</v>
       </c>
       <c r="B5" t="n">
-        <v>105853</v>
+        <v>98292</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,28 +1045,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
@@ -1145,7 +1154,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125382252</v>
+        <v>125382250</v>
       </c>
       <c r="B6" t="n">
         <v>98292</v>
@@ -1180,7 +1189,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720924</v>
+        <v>720917</v>
       </c>
       <c r="R6" t="n">
-        <v>6361826</v>
+        <v>6361832</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1266,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125382250</v>
+        <v>125382252</v>
       </c>
       <c r="B7" t="n">
         <v>98292</v>
@@ -1301,7 +1310,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1320,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720917</v>
+        <v>720924</v>
       </c>
       <c r="R7" t="n">
-        <v>6361832</v>
+        <v>6361826</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1387,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125382079</v>
+        <v>125382243</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
+        <v>105853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,47 +1408,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720903</v>
+        <v>720878</v>
       </c>
       <c r="R8" t="n">
-        <v>6361878</v>
+        <v>6361800</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,11 +1474,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Födosök i död tall</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1487,6 +1482,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382246</v>
+        <v>125382079</v>
       </c>
       <c r="B2" t="n">
-        <v>98292</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720893</v>
+        <v>720903</v>
       </c>
       <c r="R2" t="n">
-        <v>6361820</v>
+        <v>6361878</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +762,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök i död tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,11 +775,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125382079</v>
+        <v>125382246</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>98292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,35 +803,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720903</v>
+        <v>720893</v>
       </c>
       <c r="R3" t="n">
-        <v>6361878</v>
+        <v>6361820</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,11 +883,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök i död tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -896,6 +891,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382079</v>
+        <v>125382246</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>98292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720903</v>
+        <v>720893</v>
       </c>
       <c r="R2" t="n">
-        <v>6361878</v>
+        <v>6361820</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,11 +767,6 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök i död tall</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +775,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125382246</v>
+        <v>125382079</v>
       </c>
       <c r="B3" t="n">
-        <v>98292</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +808,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720893</v>
+        <v>720903</v>
       </c>
       <c r="R3" t="n">
-        <v>6361820</v>
+        <v>6361878</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,6 +883,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök i död tall</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,11 +896,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Ängsbarrskog frisk, nedom ancylusgränsvall.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125382246</v>
+        <v>125382243</v>
       </c>
       <c r="B2" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720893</v>
+        <v>720878</v>
       </c>
       <c r="R2" t="n">
-        <v>6361820</v>
+        <v>6361800</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -799,12 +780,7 @@
         <v>125382079</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125382263</v>
+        <v>125382250</v>
       </c>
       <c r="B4" t="n">
-        <v>98291</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,26 +899,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -957,7 +928,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720892</v>
+        <v>720917</v>
       </c>
       <c r="R4" t="n">
-        <v>6361887</v>
+        <v>6361832</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1033,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125382244</v>
+        <v>125382246</v>
       </c>
       <c r="B5" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1068,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1087,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720878</v>
+        <v>720893</v>
       </c>
       <c r="R5" t="n">
-        <v>6361800</v>
+        <v>6361820</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1154,15 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125382250</v>
+        <v>125382263</v>
       </c>
       <c r="B6" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1131,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1199,7 +1160,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1208,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720917</v>
+        <v>720892</v>
       </c>
       <c r="R6" t="n">
-        <v>6361832</v>
+        <v>6361887</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1278,12 +1239,7 @@
         <v>125382252</v>
       </c>
       <c r="B7" t="n">
-        <v>98292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,40 +1352,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125382243</v>
+        <v>125382244</v>
       </c>
       <c r="B8" t="n">
-        <v>105853</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Alskog Rommunds 2:1 (5), Gtl</t>
@@ -1500,6 +1465,103 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125876891</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95927</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alskog Rommunds 2:1 (5), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720745</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6361794</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125382243</v>
       </c>
       <c r="B2" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>125382250</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125382246</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>125382263</v>
       </c>
       <c r="B6" t="n">
-        <v>98346</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>125382252</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>125382244</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95934</v>
+        <v>95935</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125382243</v>
       </c>
       <c r="B2" t="n">
-        <v>105915</v>
+        <v>105918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>125382250</v>
       </c>
       <c r="B4" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125382246</v>
       </c>
       <c r="B5" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>125382263</v>
       </c>
       <c r="B6" t="n">
-        <v>98353</v>
+        <v>98356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>125382252</v>
       </c>
       <c r="B7" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>125382244</v>
       </c>
       <c r="B8" t="n">
-        <v>98354</v>
+        <v>98357</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125382243</v>
       </c>
       <c r="B2" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>125382250</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125382246</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>125382263</v>
       </c>
       <c r="B6" t="n">
-        <v>98356</v>
+        <v>98360</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>125382252</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>125382244</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125382243</v>
       </c>
       <c r="B2" t="n">
-        <v>105922</v>
+        <v>105923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>125382250</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>125382246</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>125382263</v>
       </c>
       <c r="B6" t="n">
-        <v>98360</v>
+        <v>98361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>125382252</v>
       </c>
       <c r="B7" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>125382244</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 16375-2025 artfynd.xlsx
+++ b/artfynd/A 16375-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
         <v>125876891</v>
       </c>
       <c r="B9" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
